--- a/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt2_rubricas.xlsx
@@ -1848,13 +1848,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39797895-6E28-4DFE-B663-793C27CC436C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE5FC8C-19E3-4ADB-A0B9-2CF44662B364}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE586F8F-090B-4AD5-81FE-E64FAEADF8A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B6E7EDE-57BE-4BDD-940A-C76CDC5F4D58}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8258A465-A7C3-43D9-8175-12FA4BB81358}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8686B0C-C865-4DD3-93C3-12F945EF3C7B}"/>
 </file>